--- a/WorkBot/refactor-experimental/data/orders/US Foods/US Foods_Syracuse_20251031.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/US Foods/US Foods_Syracuse_20251031.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -740,6 +740,60 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2477933</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bacon (Pre-Cooked)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>39.86</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>398.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>7132137</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>English Muffin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>34.79</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>34.79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
